--- a/design-system/scratch/roster.xlsx
+++ b/design-system/scratch/roster.xlsx
@@ -67,10 +67,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>442104959</t>
-  </si>
-  <si>
-    <t>سعود بن محمد بن ابراهيم الشدوخي</t>
+    <t>999000001</t>
+  </si>
+  <si>
+    <t>باسل أنور لطفي راشد جابر اليامي</t>
   </si>
   <si>
     <t>منتظم</t>
@@ -79,190 +79,190 @@
     <t>2</t>
   </si>
   <si>
-    <t>462103556</t>
-  </si>
-  <si>
-    <t>علي بن ابراهيم بن علي حدادي</t>
+    <t>999000002</t>
+  </si>
+  <si>
+    <t>فارس نصار نصار هلال هلال القرني</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>462109105</t>
-  </si>
-  <si>
-    <t>عبدالعزيز بن عبدالرحمن بن عبدالعزيز الجويعي</t>
+    <t>999000003</t>
+  </si>
+  <si>
+    <t>مازن راشد مراد نصار فهمي البارقي</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>462109230</t>
-  </si>
-  <si>
-    <t>يونس بن علي بن محمد حدادي</t>
+    <t>999000004</t>
+  </si>
+  <si>
+    <t>عادل راشد راشد صابر عاطف الهذلي</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>462109232</t>
-  </si>
-  <si>
-    <t>فهد بن سلطان بن ماضي العتيبي</t>
+    <t>999000005</t>
+  </si>
+  <si>
+    <t>مازن حمدان أنور عاطف راشد الوادعي</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>471103890</t>
-  </si>
-  <si>
-    <t>عبدالمجيد بن محمد بن  عبدالله الراشد</t>
+    <t>999000006</t>
+  </si>
+  <si>
+    <t>لؤي ثامر غازي عاطف فهمي القرني</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>471104932</t>
-  </si>
-  <si>
-    <t>عبدالعزيز بن محمد بن  سالم البديري المطيري</t>
+    <t>999000007</t>
+  </si>
+  <si>
+    <t>غسان فهمي راشد شاكر ضياء عاطف الكثيري</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>471105041</t>
-  </si>
-  <si>
-    <t>ثامر بن ابراهيم بن  حمد اللهيب</t>
+    <t>999000008</t>
+  </si>
+  <si>
+    <t>شادي عاطف قاسم ضياء غازي البارقي</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>471105043</t>
-  </si>
-  <si>
-    <t>عبدالسلام بن فهد بن حمود السبيعي</t>
+    <t>999000009</t>
+  </si>
+  <si>
+    <t>رائد وائل راشد وائل غازي النجدي</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>471105048</t>
-  </si>
-  <si>
-    <t>عبدالرحمن بن عبدالله بن  ضميان السبيعي العنزي</t>
+    <t>999000010</t>
+  </si>
+  <si>
+    <t>شادي بدر ضياء ضياء ضياء راشد الفيفي</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>471105050</t>
-  </si>
-  <si>
-    <t>مازن بن بشير بن  نافع العنزي</t>
+    <t>999000011</t>
+  </si>
+  <si>
+    <t>طارق لطفي ثامر حمدان قاسم الوادعي</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>471105056</t>
-  </si>
-  <si>
-    <t>ريان بن جلوي بن مسفر المطيري</t>
+    <t>999000012</t>
+  </si>
+  <si>
+    <t>جمال مراد مراد غازي حمدان البارقي</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>471105058</t>
-  </si>
-  <si>
-    <t>تركي بن سلمان بن فيصل العتيبي</t>
+    <t>999000013</t>
+  </si>
+  <si>
+    <t>وليد فهمي راشد عاطف ثامر اليامي</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>471105060</t>
-  </si>
-  <si>
-    <t>بدر بن فهد بن  سليمان السبيعي العنزي</t>
+    <t>999000014</t>
+  </si>
+  <si>
+    <t>رائد بدر سامي ياسر مراد حمدان الصاعدي</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>471105061</t>
-  </si>
-  <si>
-    <t>سلمان بن بدر بن  محمد الشثيلي المطيري</t>
+    <t>999000015</t>
+  </si>
+  <si>
+    <t>شادي ثامر هلال ثامر راشد لطفي المالكي</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>471105064</t>
-  </si>
-  <si>
-    <t>عبدالعزيز بن مطلق بن  حمد العيباني المطيري</t>
+    <t>999000016</t>
+  </si>
+  <si>
+    <t>فارس ثامر جابر شاكر ياسر ضياء الوادعي</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>471105067</t>
-  </si>
-  <si>
-    <t>فهد بن منيور بن  قريزح الضبيطي المطيري</t>
+    <t>999000017</t>
+  </si>
+  <si>
+    <t>سالم جابر سامي جابر أنور وائل الحميدي</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>471105068</t>
-  </si>
-  <si>
-    <t>فارس بن مرزوق بن  مقبل البديرى المطيرى</t>
+    <t>999000018</t>
+  </si>
+  <si>
+    <t>فارس لطفي لطفي ضياء شاكر نصار الكثيري</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>471105069</t>
-  </si>
-  <si>
-    <t>عبدالعزيز بن حمد بن  عبدالعزيز الجوف</t>
+    <t>999000019</t>
+  </si>
+  <si>
+    <t>غسان غازي فهمي أنور لطفي اليامي</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>471105074</t>
-  </si>
-  <si>
-    <t>نواف بن عبدالله بن  محمد التويجري</t>
+    <t>999000020</t>
+  </si>
+  <si>
+    <t>زياد قاسم وائل ضياء جابر الوادعي</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>471105147</t>
-  </si>
-  <si>
-    <t>سليمان بن عبدالله بن سليمان العطيوي</t>
+    <t>999000021</t>
+  </si>
+  <si>
+    <t>لؤي مراد شاكر حمدان حمدان الطلحي</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>472113211</t>
-  </si>
-  <si>
-    <t>زياد بن عبدالله بن احمد  الزعيبي</t>
+    <t>999000022</t>
+  </si>
+  <si>
+    <t>عمار ضياء أنور وائل بدر الصاعدي</t>
   </si>
 </sst>
 </file>
